--- a/scholarship_application_forms/023_scholarship_renewal_contact_form--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/023_scholarship_renewal_contact_form--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -947,185 +947,134 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>academic_status_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>academic_status_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>college</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>College</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>academic_status_choices</t>
+          <t>financial_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>student_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stable</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>student_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>unstable</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unstable</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>financial_status_choices</t>
+          <t>updated_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_status_choices</t>
+          <t>updated_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_status_choices</t>
+          <t>updated_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>updated_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>updated_status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>updated_status_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
